--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -1569,48 +1569,58 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125778094</v>
+        <v>125778932</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>98345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495171</v>
+        <v>495122</v>
       </c>
       <c r="R9" t="n">
-        <v>7006053</v>
+        <v>7006144</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1644,7 +1654,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,26 +1669,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1696,58 +1686,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125778932</v>
+        <v>125778094</v>
       </c>
       <c r="B10" t="n">
-        <v>98345</v>
+        <v>78967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495122</v>
+        <v>495171</v>
       </c>
       <c r="R10" t="n">
-        <v>7006144</v>
+        <v>7006053</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1781,7 +1761,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1796,6 +1776,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2154,38 +2154,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125778820</v>
+        <v>125778646</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>98345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2194,13 +2208,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495134</v>
+        <v>495089</v>
       </c>
       <c r="R14" t="n">
-        <v>7006068</v>
+        <v>7006086</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2234,7 +2248,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
+          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2249,26 +2263,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2286,52 +2280,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125778646</v>
+        <v>125778820</v>
       </c>
       <c r="B15" t="n">
-        <v>98345</v>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2340,13 +2320,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495089</v>
+        <v>495134</v>
       </c>
       <c r="R15" t="n">
-        <v>7006086</v>
+        <v>7006068</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2380,7 +2360,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
+          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2395,6 +2375,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125780777</v>
       </c>
       <c r="B2" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1569,58 +1569,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125778932</v>
+        <v>125778094</v>
       </c>
       <c r="B9" t="n">
-        <v>98345</v>
+        <v>78967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495122</v>
+        <v>495171</v>
       </c>
       <c r="R9" t="n">
-        <v>7006144</v>
+        <v>7006053</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1654,7 +1644,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1669,6 +1659,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1686,48 +1696,58 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125778094</v>
+        <v>125778932</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>98352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495171</v>
+        <v>495122</v>
       </c>
       <c r="R10" t="n">
-        <v>7006053</v>
+        <v>7006144</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1761,7 +1781,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1776,26 +1796,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1943,7 +1943,7 @@
         <v>125779205</v>
       </c>
       <c r="B12" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>125778852</v>
       </c>
       <c r="B13" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>125778646</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>125780666</v>
       </c>
       <c r="B16" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>125783490</v>
       </c>
       <c r="B17" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>125782390</v>
       </c>
       <c r="B20" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125778303</v>
+        <v>125780717</v>
       </c>
       <c r="B21" t="n">
         <v>78967</v>
@@ -3075,21 +3075,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495064</v>
+        <v>495098</v>
       </c>
       <c r="R21" t="n">
-        <v>7006053</v>
+        <v>7006108</v>
       </c>
       <c r="S21" t="n">
         <v>8</v>
@@ -3119,14 +3114,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Långväxta bålar med apothecier.</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3178,7 +3178,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125780717</v>
+        <v>125778303</v>
       </c>
       <c r="B22" t="n">
         <v>78967</v>
@@ -3207,16 +3207,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495098</v>
+        <v>495064</v>
       </c>
       <c r="R22" t="n">
-        <v>7006108</v>
+        <v>7006053</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3246,19 +3251,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>20:14</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>20:14</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Långväxta bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3313,7 +3313,7 @@
         <v>125804779</v>
       </c>
       <c r="B23" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>125783073</v>
       </c>
       <c r="B24" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>125804167</v>
       </c>
       <c r="B25" t="n">
-        <v>91216</v>
+        <v>91223</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>125803850</v>
       </c>
       <c r="B26" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>125783380</v>
       </c>
       <c r="B27" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>125781629</v>
       </c>
       <c r="B29" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>125804684</v>
       </c>
       <c r="B30" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>125803663</v>
       </c>
       <c r="B31" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>125780529</v>
       </c>
       <c r="B34" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>125804658</v>
       </c>
       <c r="B35" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -1422,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125782185</v>
+        <v>125778094</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,47 +1433,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494985</v>
+        <v>495171</v>
       </c>
       <c r="R8" t="n">
-        <v>7006130</v>
+        <v>7006053</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1500,24 +1490,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,7 +1511,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1546,12 +1526,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1569,48 +1549,58 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125778094</v>
+        <v>125778932</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>98352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495171</v>
+        <v>495122</v>
       </c>
       <c r="R9" t="n">
-        <v>7006053</v>
+        <v>7006144</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1644,7 +1634,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,26 +1649,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1696,38 +1666,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125778932</v>
+        <v>125782185</v>
       </c>
       <c r="B10" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1737,17 +1707,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495122</v>
+        <v>494985</v>
       </c>
       <c r="R10" t="n">
-        <v>7006144</v>
+        <v>7006130</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1774,14 +1744,24 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1795,7 +1775,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -3046,7 +3046,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125780717</v>
+        <v>125778303</v>
       </c>
       <c r="B21" t="n">
         <v>78967</v>
@@ -3075,16 +3075,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495098</v>
+        <v>495064</v>
       </c>
       <c r="R21" t="n">
-        <v>7006108</v>
+        <v>7006053</v>
       </c>
       <c r="S21" t="n">
         <v>8</v>
@@ -3114,19 +3119,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>20:14</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>20:14</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långväxta bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3178,7 +3178,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125778303</v>
+        <v>125780717</v>
       </c>
       <c r="B22" t="n">
         <v>78967</v>
@@ -3207,21 +3207,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495064</v>
+        <v>495098</v>
       </c>
       <c r="R22" t="n">
-        <v>7006053</v>
+        <v>7006108</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3251,14 +3246,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Långväxta bålar med apothecier.</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4240,58 +4240,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125804684</v>
+        <v>125804911</v>
       </c>
       <c r="B30" t="n">
-        <v>98352</v>
+        <v>78967</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495194</v>
+        <v>495201</v>
       </c>
       <c r="R30" t="n">
-        <v>7006084</v>
+        <v>7006107</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4320,7 +4310,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4330,7 +4320,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4345,6 +4335,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4362,7 +4372,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125803663</v>
+        <v>125804684</v>
       </c>
       <c r="B31" t="n">
         <v>98352</v>
@@ -4396,19 +4406,24 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495111</v>
+        <v>495194</v>
       </c>
       <c r="R31" t="n">
-        <v>7006101</v>
+        <v>7006084</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4437,7 +4452,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4447,7 +4462,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4479,48 +4494,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125804911</v>
+        <v>125803663</v>
       </c>
       <c r="B32" t="n">
-        <v>78967</v>
+        <v>98352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495201</v>
+        <v>495111</v>
       </c>
       <c r="R32" t="n">
-        <v>7006107</v>
+        <v>7006101</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4549,7 +4569,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4559,7 +4579,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4574,26 +4594,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -3046,7 +3046,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125778303</v>
+        <v>125780717</v>
       </c>
       <c r="B21" t="n">
         <v>78967</v>
@@ -3075,21 +3075,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495064</v>
+        <v>495098</v>
       </c>
       <c r="R21" t="n">
-        <v>7006053</v>
+        <v>7006108</v>
       </c>
       <c r="S21" t="n">
         <v>8</v>
@@ -3119,14 +3114,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Långväxta bålar med apothecier.</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3178,7 +3178,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125780717</v>
+        <v>125778303</v>
       </c>
       <c r="B22" t="n">
         <v>78967</v>
@@ -3207,16 +3207,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495098</v>
+        <v>495064</v>
       </c>
       <c r="R22" t="n">
-        <v>7006108</v>
+        <v>7006053</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3246,19 +3251,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>20:14</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>20:14</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Långväxta bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3310,58 +3310,62 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125804779</v>
+        <v>125783073</v>
       </c>
       <c r="B23" t="n">
-        <v>98352</v>
+        <v>98332</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495257</v>
+        <v>495060</v>
       </c>
       <c r="R23" t="n">
-        <v>7006101</v>
+        <v>7006169</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3385,22 +3389,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 300 plantor och 1 vinterståndare inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3414,7 +3423,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3432,62 +3441,58 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125783073</v>
+        <v>125804779</v>
       </c>
       <c r="B24" t="n">
-        <v>98331</v>
+        <v>98353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495060</v>
+        <v>495257</v>
       </c>
       <c r="R24" t="n">
-        <v>7006169</v>
+        <v>7006101</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3511,27 +3516,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>21:29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minst 300 plantor och 1 vinterståndare inom ca 3 m2 yta.</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3566,7 +3566,7 @@
         <v>125804167</v>
       </c>
       <c r="B25" t="n">
-        <v>91223</v>
+        <v>91224</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>125803850</v>
       </c>
       <c r="B26" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>125783380</v>
       </c>
       <c r="B27" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3967,48 +3967,67 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125803426</v>
+        <v>125781629</v>
       </c>
       <c r="B28" t="n">
-        <v>78967</v>
+        <v>98332</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495064</v>
+        <v>495033</v>
       </c>
       <c r="R28" t="n">
-        <v>7006141</v>
+        <v>7006135</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4032,27 +4051,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4067,26 +4086,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4104,67 +4103,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125781629</v>
+        <v>125803426</v>
       </c>
       <c r="B29" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495033</v>
+        <v>495064</v>
       </c>
       <c r="R29" t="n">
-        <v>7006135</v>
+        <v>7006141</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4188,27 +4168,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4223,6 +4203,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4243,7 +4243,7 @@
         <v>125804911</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125804684</v>
+        <v>125803663</v>
       </c>
       <c r="B31" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4406,24 +4406,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495194</v>
+        <v>495111</v>
       </c>
       <c r="R31" t="n">
-        <v>7006084</v>
+        <v>7006101</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4452,7 +4447,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4462,7 +4457,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4494,10 +4489,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125803663</v>
+        <v>125804684</v>
       </c>
       <c r="B32" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4528,19 +4523,24 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495111</v>
+        <v>495194</v>
       </c>
       <c r="R32" t="n">
-        <v>7006101</v>
+        <v>7006084</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4611,48 +4611,62 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125805258</v>
+        <v>125780529</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>98332</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495123</v>
+        <v>495099</v>
       </c>
       <c r="R33" t="n">
-        <v>7006163</v>
+        <v>7006156</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4676,22 +4690,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4706,26 +4725,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4743,62 +4742,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125780529</v>
+        <v>125805258</v>
       </c>
       <c r="B34" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495099</v>
+        <v>495123</v>
       </c>
       <c r="R34" t="n">
-        <v>7006156</v>
+        <v>7006163</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4822,27 +4807,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:03</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4857,6 +4837,26 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4877,7 +4877,7 @@
         <v>125804658</v>
       </c>
       <c r="B35" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125780777</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125782273</v>
       </c>
       <c r="B3" t="n">
-        <v>80106</v>
+        <v>80107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>125779100</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>125778168</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>125782341</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>125783644</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>125778094</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,38 +1549,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125778932</v>
+        <v>125782185</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495122</v>
+        <v>494985</v>
       </c>
       <c r="R9" t="n">
-        <v>7006144</v>
+        <v>7006130</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1627,14 +1627,24 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,7 +1658,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1666,38 +1696,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125782185</v>
+        <v>125778932</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>98355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1707,17 +1737,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494985</v>
+        <v>495122</v>
       </c>
       <c r="R10" t="n">
-        <v>7006130</v>
+        <v>7006144</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1744,24 +1774,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1775,27 +1795,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1816,7 +1816,7 @@
         <v>125778369</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>125779205</v>
       </c>
       <c r="B12" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>125778852</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2154,52 +2154,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125778646</v>
+        <v>125778820</v>
       </c>
       <c r="B14" t="n">
-        <v>98352</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2208,13 +2194,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495089</v>
+        <v>495134</v>
       </c>
       <c r="R14" t="n">
-        <v>7006086</v>
+        <v>7006068</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2248,7 +2234,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
+          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2263,6 +2249,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2280,38 +2286,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125778820</v>
+        <v>125778646</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>98355</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2320,13 +2340,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495134</v>
+        <v>495089</v>
       </c>
       <c r="R15" t="n">
-        <v>7006068</v>
+        <v>7006086</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2360,7 +2380,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
+          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2375,26 +2395,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2415,7 +2415,7 @@
         <v>125780666</v>
       </c>
       <c r="B16" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>125783490</v>
       </c>
       <c r="B17" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>125782724</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>125781018</v>
       </c>
       <c r="B19" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>125782390</v>
       </c>
       <c r="B20" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125780717</v>
+        <v>125778303</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3075,16 +3075,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495098</v>
+        <v>495064</v>
       </c>
       <c r="R21" t="n">
-        <v>7006108</v>
+        <v>7006053</v>
       </c>
       <c r="S21" t="n">
         <v>8</v>
@@ -3114,19 +3119,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>20:14</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>20:14</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långväxta bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3178,10 +3178,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125778303</v>
+        <v>125780717</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3207,21 +3207,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495064</v>
+        <v>495098</v>
       </c>
       <c r="R22" t="n">
-        <v>7006053</v>
+        <v>7006108</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3251,14 +3246,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Långväxta bålar med apothecier.</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3313,7 +3313,7 @@
         <v>125783073</v>
       </c>
       <c r="B23" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>125804779</v>
       </c>
       <c r="B24" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>125803850</v>
       </c>
       <c r="B26" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>125783380</v>
       </c>
       <c r="B27" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3967,67 +3967,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125781629</v>
+        <v>125803426</v>
       </c>
       <c r="B28" t="n">
-        <v>98332</v>
+        <v>78968</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495033</v>
+        <v>495064</v>
       </c>
       <c r="R28" t="n">
-        <v>7006135</v>
+        <v>7006141</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4051,27 +4032,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4086,6 +4067,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4103,48 +4104,67 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125803426</v>
+        <v>125781629</v>
       </c>
       <c r="B29" t="n">
-        <v>78968</v>
+        <v>98334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495064</v>
+        <v>495033</v>
       </c>
       <c r="R29" t="n">
-        <v>7006141</v>
+        <v>7006135</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4168,27 +4188,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4203,26 +4223,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4375,7 +4375,7 @@
         <v>125803663</v>
       </c>
       <c r="B31" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>125804684</v>
       </c>
       <c r="B32" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4611,62 +4611,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125780529</v>
+        <v>125805258</v>
       </c>
       <c r="B33" t="n">
-        <v>98332</v>
+        <v>78968</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495099</v>
+        <v>495123</v>
       </c>
       <c r="R33" t="n">
-        <v>7006156</v>
+        <v>7006163</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4690,27 +4676,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:03</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4725,6 +4706,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4742,48 +4743,62 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125805258</v>
+        <v>125780529</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>98334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495123</v>
+        <v>495099</v>
       </c>
       <c r="R34" t="n">
-        <v>7006163</v>
+        <v>7006156</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4807,22 +4822,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4837,26 +4857,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4877,7 +4877,7 @@
         <v>125804658</v>
       </c>
       <c r="B35" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -1422,48 +1422,58 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125778094</v>
+        <v>125778932</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>98355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495171</v>
+        <v>495122</v>
       </c>
       <c r="R8" t="n">
-        <v>7006053</v>
+        <v>7006144</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1497,7 +1507,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,26 +1522,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1549,10 +1539,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125782185</v>
+        <v>125778094</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,47 +1550,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494985</v>
+        <v>495171</v>
       </c>
       <c r="R9" t="n">
-        <v>7006130</v>
+        <v>7006053</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1627,24 +1607,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1658,7 +1628,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1673,12 +1643,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1696,38 +1666,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125778932</v>
+        <v>125782185</v>
       </c>
       <c r="B10" t="n">
-        <v>98355</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1737,17 +1707,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495122</v>
+        <v>494985</v>
       </c>
       <c r="R10" t="n">
-        <v>7006144</v>
+        <v>7006130</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1774,14 +1744,24 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1795,7 +1775,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2661,48 +2661,67 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125782724</v>
+        <v>125781018</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>58020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495062</v>
+        <v>495061</v>
       </c>
       <c r="R18" t="n">
-        <v>7006173</v>
+        <v>7006152</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2731,7 +2750,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2741,12 +2760,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>21:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2761,26 +2775,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2798,67 +2792,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125781018</v>
+        <v>125782724</v>
       </c>
       <c r="B19" t="n">
-        <v>58020</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495061</v>
+        <v>495062</v>
       </c>
       <c r="R19" t="n">
-        <v>7006152</v>
+        <v>7006173</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2887,7 +2862,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2897,7 +2872,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2912,6 +2892,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3310,62 +3310,58 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125783073</v>
+        <v>125804779</v>
       </c>
       <c r="B23" t="n">
-        <v>98334</v>
+        <v>98355</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495060</v>
+        <v>495257</v>
       </c>
       <c r="R23" t="n">
-        <v>7006169</v>
+        <v>7006101</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3389,27 +3385,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>21:29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minst 300 plantor och 1 vinterståndare inom ca 3 m2 yta.</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3423,7 +3414,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3441,58 +3432,62 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125804779</v>
+        <v>125783073</v>
       </c>
       <c r="B24" t="n">
-        <v>98355</v>
+        <v>98334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495257</v>
+        <v>495060</v>
       </c>
       <c r="R24" t="n">
-        <v>7006101</v>
+        <v>7006169</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3516,22 +3511,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minst 300 plantor och 1 vinterståndare inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125780777</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125782273</v>
       </c>
       <c r="B3" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>125779100</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>125778168</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>125782341</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>125783644</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1422,58 +1422,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125778932</v>
+        <v>125778094</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495122</v>
+        <v>495171</v>
       </c>
       <c r="R8" t="n">
-        <v>7006144</v>
+        <v>7006053</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1507,7 +1497,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,6 +1512,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1539,10 +1549,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125778094</v>
+        <v>125782185</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,37 +1560,47 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495171</v>
+        <v>494985</v>
       </c>
       <c r="R9" t="n">
-        <v>7006053</v>
+        <v>7006130</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,14 +1627,24 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,7 +1658,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1643,12 +1673,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1666,38 +1696,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125782185</v>
+        <v>125778932</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1707,17 +1737,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494985</v>
+        <v>495122</v>
       </c>
       <c r="R10" t="n">
-        <v>7006130</v>
+        <v>7006144</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1744,24 +1774,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1775,27 +1795,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1816,7 +1816,7 @@
         <v>125778369</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>125779205</v>
       </c>
       <c r="B12" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>125778852</v>
       </c>
       <c r="B13" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2154,38 +2154,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125778820</v>
+        <v>125778646</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>98359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2194,13 +2208,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495134</v>
+        <v>495089</v>
       </c>
       <c r="R14" t="n">
-        <v>7006068</v>
+        <v>7006086</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2234,7 +2248,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
+          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2249,26 +2263,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2286,52 +2280,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125778646</v>
+        <v>125778820</v>
       </c>
       <c r="B15" t="n">
-        <v>98355</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2340,13 +2320,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495089</v>
+        <v>495134</v>
       </c>
       <c r="R15" t="n">
-        <v>7006086</v>
+        <v>7006068</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2380,7 +2360,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
+          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2395,6 +2375,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2415,7 +2415,7 @@
         <v>125780666</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>125783490</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2661,67 +2661,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125781018</v>
+        <v>125782724</v>
       </c>
       <c r="B18" t="n">
-        <v>58020</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495061</v>
+        <v>495062</v>
       </c>
       <c r="R18" t="n">
-        <v>7006152</v>
+        <v>7006173</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2750,7 +2731,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2760,7 +2741,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2775,6 +2761,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2792,48 +2798,67 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125782724</v>
+        <v>125781018</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>58020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495062</v>
+        <v>495061</v>
       </c>
       <c r="R19" t="n">
-        <v>7006173</v>
+        <v>7006152</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2862,7 +2887,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2872,12 +2897,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>21:21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2892,26 +2912,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2932,7 +2932,7 @@
         <v>125782390</v>
       </c>
       <c r="B20" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>125778303</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>125780717</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>125804779</v>
       </c>
       <c r="B23" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>125783073</v>
       </c>
       <c r="B24" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>125804167</v>
       </c>
       <c r="B25" t="n">
-        <v>91224</v>
+        <v>91228</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>125803850</v>
       </c>
       <c r="B26" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>125783380</v>
       </c>
       <c r="B27" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>125803426</v>
       </c>
       <c r="B28" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>125781629</v>
       </c>
       <c r="B29" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>125804911</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125803663</v>
+        <v>125804684</v>
       </c>
       <c r="B31" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4406,19 +4406,24 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495111</v>
+        <v>495194</v>
       </c>
       <c r="R31" t="n">
-        <v>7006101</v>
+        <v>7006084</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4447,7 +4452,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4457,7 +4462,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4489,10 +4494,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125804684</v>
+        <v>125803663</v>
       </c>
       <c r="B32" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4523,24 +4528,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495194</v>
+        <v>495111</v>
       </c>
       <c r="R32" t="n">
-        <v>7006084</v>
+        <v>7006101</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4611,48 +4611,62 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125805258</v>
+        <v>125780529</v>
       </c>
       <c r="B33" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495123</v>
+        <v>495099</v>
       </c>
       <c r="R33" t="n">
-        <v>7006163</v>
+        <v>7006156</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4676,22 +4690,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4706,26 +4725,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4743,62 +4742,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125780529</v>
+        <v>125805258</v>
       </c>
       <c r="B34" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495099</v>
+        <v>495123</v>
       </c>
       <c r="R34" t="n">
-        <v>7006156</v>
+        <v>7006163</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4822,27 +4807,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:03</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4857,6 +4837,26 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4877,7 +4877,7 @@
         <v>125804658</v>
       </c>
       <c r="B35" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -2154,52 +2154,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125778646</v>
+        <v>125778820</v>
       </c>
       <c r="B14" t="n">
-        <v>98359</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2208,13 +2194,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495089</v>
+        <v>495134</v>
       </c>
       <c r="R14" t="n">
-        <v>7006086</v>
+        <v>7006068</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2248,7 +2234,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
+          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2263,6 +2249,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2280,38 +2286,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125778820</v>
+        <v>125778646</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>98359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2320,13 +2340,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495134</v>
+        <v>495089</v>
       </c>
       <c r="R15" t="n">
-        <v>7006068</v>
+        <v>7006086</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2360,7 +2380,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
+          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2375,26 +2395,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -3967,48 +3967,67 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125803426</v>
+        <v>125781629</v>
       </c>
       <c r="B28" t="n">
-        <v>78972</v>
+        <v>98338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495064</v>
+        <v>495033</v>
       </c>
       <c r="R28" t="n">
-        <v>7006141</v>
+        <v>7006135</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4032,27 +4051,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4067,26 +4086,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4104,67 +4103,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125781629</v>
+        <v>125803426</v>
       </c>
       <c r="B29" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495033</v>
+        <v>495064</v>
       </c>
       <c r="R29" t="n">
-        <v>7006135</v>
+        <v>7006141</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4188,27 +4168,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4223,6 +4203,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125780777</v>
       </c>
       <c r="B2" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1422,48 +1422,58 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125778094</v>
+        <v>125778932</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495171</v>
+        <v>495122</v>
       </c>
       <c r="R8" t="n">
-        <v>7006053</v>
+        <v>7006144</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1497,7 +1507,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,26 +1522,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1696,58 +1686,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125778932</v>
+        <v>125778094</v>
       </c>
       <c r="B10" t="n">
-        <v>98359</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495122</v>
+        <v>495171</v>
       </c>
       <c r="R10" t="n">
-        <v>7006144</v>
+        <v>7006053</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1781,7 +1761,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1796,6 +1776,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1943,7 +1943,7 @@
         <v>125779205</v>
       </c>
       <c r="B12" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>125778852</v>
       </c>
       <c r="B13" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>125778646</v>
       </c>
       <c r="B15" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>125780666</v>
       </c>
       <c r="B16" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>125783490</v>
       </c>
       <c r="B17" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>125782390</v>
       </c>
       <c r="B20" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3310,58 +3310,62 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125804779</v>
+        <v>125783073</v>
       </c>
       <c r="B23" t="n">
-        <v>98359</v>
+        <v>98339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495257</v>
+        <v>495060</v>
       </c>
       <c r="R23" t="n">
-        <v>7006101</v>
+        <v>7006169</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3385,22 +3389,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 300 plantor och 1 vinterståndare inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3414,7 +3423,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3432,62 +3441,58 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125783073</v>
+        <v>125804779</v>
       </c>
       <c r="B24" t="n">
-        <v>98338</v>
+        <v>98360</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495060</v>
+        <v>495257</v>
       </c>
       <c r="R24" t="n">
-        <v>7006169</v>
+        <v>7006101</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3511,27 +3516,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>21:29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minst 300 plantor och 1 vinterståndare inom ca 3 m2 yta.</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3717,7 +3717,7 @@
         <v>125803850</v>
       </c>
       <c r="B26" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>125783380</v>
       </c>
       <c r="B27" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>125781629</v>
       </c>
       <c r="B28" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125804684</v>
+        <v>125803663</v>
       </c>
       <c r="B31" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4406,24 +4406,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495194</v>
+        <v>495111</v>
       </c>
       <c r="R31" t="n">
-        <v>7006084</v>
+        <v>7006101</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4452,7 +4447,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4462,7 +4457,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4494,10 +4489,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125803663</v>
+        <v>125804684</v>
       </c>
       <c r="B32" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4528,19 +4523,24 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495111</v>
+        <v>495194</v>
       </c>
       <c r="R32" t="n">
-        <v>7006101</v>
+        <v>7006084</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4611,62 +4611,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125780529</v>
+        <v>125805258</v>
       </c>
       <c r="B33" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495099</v>
+        <v>495123</v>
       </c>
       <c r="R33" t="n">
-        <v>7006156</v>
+        <v>7006163</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4690,27 +4676,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:03</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4725,6 +4706,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4742,48 +4743,62 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125805258</v>
+        <v>125780529</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495123</v>
+        <v>495099</v>
       </c>
       <c r="R34" t="n">
-        <v>7006163</v>
+        <v>7006156</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4807,22 +4822,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4837,26 +4857,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4877,7 +4877,7 @@
         <v>125804658</v>
       </c>
       <c r="B35" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -4611,48 +4611,62 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125805258</v>
+        <v>125780529</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495123</v>
+        <v>495099</v>
       </c>
       <c r="R33" t="n">
-        <v>7006163</v>
+        <v>7006156</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4676,22 +4690,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4706,26 +4725,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4743,62 +4742,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125780529</v>
+        <v>125805258</v>
       </c>
       <c r="B34" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495099</v>
+        <v>495123</v>
       </c>
       <c r="R34" t="n">
-        <v>7006156</v>
+        <v>7006163</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4822,27 +4807,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:03</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4857,6 +4837,26 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -1422,38 +1422,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125778932</v>
+        <v>125782185</v>
       </c>
       <c r="B8" t="n">
-        <v>98360</v>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495122</v>
+        <v>494985</v>
       </c>
       <c r="R8" t="n">
-        <v>7006144</v>
+        <v>7006130</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1500,14 +1500,24 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,7 +1531,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1539,10 +1569,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125782185</v>
+        <v>125778094</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,47 +1580,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494985</v>
+        <v>495171</v>
       </c>
       <c r="R9" t="n">
-        <v>7006130</v>
+        <v>7006053</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1617,24 +1637,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,7 +1658,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1663,12 +1673,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1686,48 +1696,58 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125778094</v>
+        <v>125778932</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495171</v>
+        <v>495122</v>
       </c>
       <c r="R10" t="n">
-        <v>7006053</v>
+        <v>7006144</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1761,7 +1781,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1776,26 +1796,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2661,48 +2661,67 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125782724</v>
+        <v>125781018</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>58020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495062</v>
+        <v>495061</v>
       </c>
       <c r="R18" t="n">
-        <v>7006173</v>
+        <v>7006152</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2731,7 +2750,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2741,12 +2760,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>21:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2761,26 +2775,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2798,67 +2792,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125781018</v>
+        <v>125782724</v>
       </c>
       <c r="B19" t="n">
-        <v>58020</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495061</v>
+        <v>495062</v>
       </c>
       <c r="R19" t="n">
-        <v>7006152</v>
+        <v>7006173</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2887,7 +2862,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2897,7 +2872,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2912,6 +2892,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125780777</v>
       </c>
       <c r="B2" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125782273</v>
       </c>
       <c r="B3" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>125779100</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>125778168</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>125782341</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>125783644</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>125782185</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1569,48 +1569,58 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125778094</v>
+        <v>125778932</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>98362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495171</v>
+        <v>495122</v>
       </c>
       <c r="R9" t="n">
-        <v>7006053</v>
+        <v>7006144</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1644,7 +1654,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,26 +1669,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1696,58 +1686,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125778932</v>
+        <v>125778094</v>
       </c>
       <c r="B10" t="n">
-        <v>98360</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495122</v>
+        <v>495171</v>
       </c>
       <c r="R10" t="n">
-        <v>7006144</v>
+        <v>7006053</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1781,7 +1761,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1796,6 +1776,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1816,7 +1816,7 @@
         <v>125778369</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125779205</v>
+        <v>125778852</v>
       </c>
       <c r="B12" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495123</v>
+        <v>495132</v>
       </c>
       <c r="R12" t="n">
-        <v>7006176</v>
+        <v>7006134</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125778852</v>
+        <v>125779205</v>
       </c>
       <c r="B13" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495132</v>
+        <v>495123</v>
       </c>
       <c r="R13" t="n">
-        <v>7006134</v>
+        <v>7006176</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>125778820</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>125778646</v>
       </c>
       <c r="B15" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>125780666</v>
       </c>
       <c r="B16" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>125783490</v>
       </c>
       <c r="B17" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2661,67 +2661,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125781018</v>
+        <v>125782724</v>
       </c>
       <c r="B18" t="n">
-        <v>58020</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495061</v>
+        <v>495062</v>
       </c>
       <c r="R18" t="n">
-        <v>7006152</v>
+        <v>7006173</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2750,7 +2731,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2760,7 +2741,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2775,6 +2761,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2792,48 +2798,67 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125782724</v>
+        <v>125781018</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>58021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495062</v>
+        <v>495061</v>
       </c>
       <c r="R19" t="n">
-        <v>7006173</v>
+        <v>7006152</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2862,7 +2887,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2872,12 +2897,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>21:21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2892,26 +2912,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2932,7 +2932,7 @@
         <v>125782390</v>
       </c>
       <c r="B20" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>125778303</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>125780717</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>125783073</v>
       </c>
       <c r="B23" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>125804779</v>
       </c>
       <c r="B24" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>125804167</v>
       </c>
       <c r="B25" t="n">
-        <v>91228</v>
+        <v>91230</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>125803850</v>
       </c>
       <c r="B26" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>125783380</v>
       </c>
       <c r="B27" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3967,67 +3967,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125781629</v>
+        <v>125803426</v>
       </c>
       <c r="B28" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495033</v>
+        <v>495064</v>
       </c>
       <c r="R28" t="n">
-        <v>7006135</v>
+        <v>7006141</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4051,27 +4032,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4086,6 +4067,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4103,48 +4104,67 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125803426</v>
+        <v>125781629</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495064</v>
+        <v>495033</v>
       </c>
       <c r="R29" t="n">
-        <v>7006141</v>
+        <v>7006135</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4168,27 +4188,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4203,26 +4223,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4243,7 +4243,7 @@
         <v>125804911</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125803663</v>
+        <v>125804684</v>
       </c>
       <c r="B31" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4406,19 +4406,24 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495111</v>
+        <v>495194</v>
       </c>
       <c r="R31" t="n">
-        <v>7006101</v>
+        <v>7006084</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4447,7 +4452,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4457,7 +4462,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4489,10 +4494,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125804684</v>
+        <v>125803663</v>
       </c>
       <c r="B32" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4523,24 +4528,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495194</v>
+        <v>495111</v>
       </c>
       <c r="R32" t="n">
-        <v>7006084</v>
+        <v>7006101</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4614,7 +4614,7 @@
         <v>125780529</v>
       </c>
       <c r="B33" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>125805258</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>125804658</v>
       </c>
       <c r="B35" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -1422,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125782185</v>
+        <v>125778094</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,47 +1433,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494985</v>
+        <v>495171</v>
       </c>
       <c r="R8" t="n">
-        <v>7006130</v>
+        <v>7006053</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1500,24 +1490,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,7 +1511,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1546,12 +1526,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1569,38 +1549,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125778932</v>
+        <v>125782185</v>
       </c>
       <c r="B9" t="n">
-        <v>98362</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1610,17 +1590,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495122</v>
+        <v>494985</v>
       </c>
       <c r="R9" t="n">
-        <v>7006144</v>
+        <v>7006130</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1647,14 +1627,24 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1668,7 +1658,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1686,48 +1696,58 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125778094</v>
+        <v>125778932</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>98362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495171</v>
+        <v>495122</v>
       </c>
       <c r="R10" t="n">
-        <v>7006053</v>
+        <v>7006144</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1761,7 +1781,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1776,26 +1796,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125780777</v>
       </c>
       <c r="B2" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125778094</v>
+        <v>125782185</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,37 +1433,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495171</v>
+        <v>494985</v>
       </c>
       <c r="R8" t="n">
-        <v>7006053</v>
+        <v>7006130</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1490,14 +1500,24 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,7 +1531,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1526,12 +1546,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1549,38 +1569,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125782185</v>
+        <v>125778932</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>98364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1590,17 +1610,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494985</v>
+        <v>495122</v>
       </c>
       <c r="R9" t="n">
-        <v>7006130</v>
+        <v>7006144</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1627,24 +1647,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1658,27 +1668,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1696,58 +1686,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125778932</v>
+        <v>125778094</v>
       </c>
       <c r="B10" t="n">
-        <v>98362</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495122</v>
+        <v>495171</v>
       </c>
       <c r="R10" t="n">
-        <v>7006144</v>
+        <v>7006053</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1781,7 +1761,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1796,6 +1776,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125778852</v>
+        <v>125779205</v>
       </c>
       <c r="B12" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495132</v>
+        <v>495123</v>
       </c>
       <c r="R12" t="n">
-        <v>7006134</v>
+        <v>7006176</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125779205</v>
+        <v>125778852</v>
       </c>
       <c r="B13" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495123</v>
+        <v>495132</v>
       </c>
       <c r="R13" t="n">
-        <v>7006176</v>
+        <v>7006134</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>125778646</v>
       </c>
       <c r="B15" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>125780666</v>
       </c>
       <c r="B16" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>125783490</v>
       </c>
       <c r="B17" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>125782390</v>
       </c>
       <c r="B20" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>125783073</v>
       </c>
       <c r="B23" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>125804779</v>
       </c>
       <c r="B24" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>125804167</v>
       </c>
       <c r="B25" t="n">
-        <v>91230</v>
+        <v>91232</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>125803850</v>
       </c>
       <c r="B26" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>125783380</v>
       </c>
       <c r="B27" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3967,48 +3967,67 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125803426</v>
+        <v>125781629</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495064</v>
+        <v>495033</v>
       </c>
       <c r="R28" t="n">
-        <v>7006141</v>
+        <v>7006135</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4032,27 +4051,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4067,26 +4086,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4104,67 +4103,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125781629</v>
+        <v>125803426</v>
       </c>
       <c r="B29" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495033</v>
+        <v>495064</v>
       </c>
       <c r="R29" t="n">
-        <v>7006135</v>
+        <v>7006141</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4188,27 +4168,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4223,6 +4203,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4375,7 +4375,7 @@
         <v>125804684</v>
       </c>
       <c r="B31" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>125803663</v>
       </c>
       <c r="B32" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>125780529</v>
       </c>
       <c r="B33" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>125804658</v>
       </c>
       <c r="B35" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -2661,48 +2661,67 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125782724</v>
+        <v>125781018</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495062</v>
+        <v>495061</v>
       </c>
       <c r="R18" t="n">
-        <v>7006173</v>
+        <v>7006152</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2731,7 +2750,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2741,12 +2760,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>21:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2761,26 +2775,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2798,67 +2792,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125781018</v>
+        <v>125782724</v>
       </c>
       <c r="B19" t="n">
-        <v>58021</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495061</v>
+        <v>495062</v>
       </c>
       <c r="R19" t="n">
-        <v>7006152</v>
+        <v>7006173</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2887,7 +2862,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2897,7 +2872,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2912,6 +2892,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -4240,48 +4240,58 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125804911</v>
+        <v>125804684</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>98364</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495201</v>
+        <v>495194</v>
       </c>
       <c r="R30" t="n">
-        <v>7006107</v>
+        <v>7006084</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4310,7 +4320,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4320,7 +4330,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4335,26 +4345,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4372,7 +4362,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125804684</v>
+        <v>125803663</v>
       </c>
       <c r="B31" t="n">
         <v>98364</v>
@@ -4406,24 +4396,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495194</v>
+        <v>495111</v>
       </c>
       <c r="R31" t="n">
-        <v>7006084</v>
+        <v>7006101</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4452,7 +4437,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4462,7 +4447,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4494,53 +4479,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125803663</v>
+        <v>125804911</v>
       </c>
       <c r="B32" t="n">
-        <v>98364</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495111</v>
+        <v>495201</v>
       </c>
       <c r="R32" t="n">
-        <v>7006101</v>
+        <v>7006107</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4569,7 +4549,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4579,7 +4559,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4594,6 +4574,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125780777</v>
       </c>
       <c r="B2" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125782185</v>
+        <v>125778094</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,47 +1433,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494985</v>
+        <v>495171</v>
       </c>
       <c r="R8" t="n">
-        <v>7006130</v>
+        <v>7006053</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1500,24 +1490,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,7 +1511,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1546,12 +1526,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1569,38 +1549,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125778932</v>
+        <v>125782185</v>
       </c>
       <c r="B9" t="n">
-        <v>98364</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1610,17 +1590,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495122</v>
+        <v>494985</v>
       </c>
       <c r="R9" t="n">
-        <v>7006144</v>
+        <v>7006130</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1647,14 +1627,24 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1668,7 +1658,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1686,48 +1696,58 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125778094</v>
+        <v>125778932</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>98366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495171</v>
+        <v>495122</v>
       </c>
       <c r="R10" t="n">
-        <v>7006053</v>
+        <v>7006144</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1761,7 +1781,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1776,26 +1796,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1943,7 +1943,7 @@
         <v>125779205</v>
       </c>
       <c r="B12" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>125778852</v>
       </c>
       <c r="B13" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>125778646</v>
       </c>
       <c r="B15" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>125780666</v>
       </c>
       <c r="B16" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>125783490</v>
       </c>
       <c r="B17" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>125782390</v>
       </c>
       <c r="B20" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3310,62 +3310,58 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125783073</v>
+        <v>125804779</v>
       </c>
       <c r="B23" t="n">
-        <v>98343</v>
+        <v>98366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495060</v>
+        <v>495257</v>
       </c>
       <c r="R23" t="n">
-        <v>7006169</v>
+        <v>7006101</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3389,27 +3385,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>21:29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minst 300 plantor och 1 vinterståndare inom ca 3 m2 yta.</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3423,7 +3414,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3441,58 +3432,62 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125804779</v>
+        <v>125783073</v>
       </c>
       <c r="B24" t="n">
-        <v>98364</v>
+        <v>98345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495257</v>
+        <v>495060</v>
       </c>
       <c r="R24" t="n">
-        <v>7006101</v>
+        <v>7006169</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3516,22 +3511,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minst 300 plantor och 1 vinterståndare inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3566,7 +3566,7 @@
         <v>125804167</v>
       </c>
       <c r="B25" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>125803850</v>
       </c>
       <c r="B26" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>125783380</v>
       </c>
       <c r="B27" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3967,67 +3967,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125781629</v>
+        <v>125803426</v>
       </c>
       <c r="B28" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495033</v>
+        <v>495064</v>
       </c>
       <c r="R28" t="n">
-        <v>7006135</v>
+        <v>7006141</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4051,27 +4032,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4086,6 +4067,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4103,48 +4104,67 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125803426</v>
+        <v>125781629</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495064</v>
+        <v>495033</v>
       </c>
       <c r="R29" t="n">
-        <v>7006141</v>
+        <v>7006135</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4168,27 +4188,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4203,26 +4223,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4243,7 +4243,7 @@
         <v>125804684</v>
       </c>
       <c r="B30" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>125803663</v>
       </c>
       <c r="B31" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4611,62 +4611,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125780529</v>
+        <v>125805258</v>
       </c>
       <c r="B33" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495099</v>
+        <v>495123</v>
       </c>
       <c r="R33" t="n">
-        <v>7006156</v>
+        <v>7006163</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4690,27 +4676,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:03</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4725,6 +4706,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4742,48 +4743,62 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125805258</v>
+        <v>125780529</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495123</v>
+        <v>495099</v>
       </c>
       <c r="R34" t="n">
-        <v>7006163</v>
+        <v>7006156</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4807,22 +4822,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4837,26 +4857,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4877,7 +4877,7 @@
         <v>125804658</v>
       </c>
       <c r="B35" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -1422,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125778094</v>
+        <v>125782185</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,37 +1433,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495171</v>
+        <v>494985</v>
       </c>
       <c r="R8" t="n">
-        <v>7006053</v>
+        <v>7006130</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1490,14 +1500,24 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,7 +1531,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1526,12 +1546,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1549,10 +1569,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125782185</v>
+        <v>125778094</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,47 +1580,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494985</v>
+        <v>495171</v>
       </c>
       <c r="R9" t="n">
-        <v>7006130</v>
+        <v>7006053</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1627,24 +1637,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2154,38 +2154,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125778820</v>
+        <v>125778646</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>98366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2194,13 +2208,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495134</v>
+        <v>495089</v>
       </c>
       <c r="R14" t="n">
-        <v>7006068</v>
+        <v>7006086</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2234,7 +2248,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
+          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2249,26 +2263,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2286,52 +2280,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125778646</v>
+        <v>125778820</v>
       </c>
       <c r="B15" t="n">
-        <v>98366</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2340,13 +2320,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495089</v>
+        <v>495134</v>
       </c>
       <c r="R15" t="n">
-        <v>7006086</v>
+        <v>7006068</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2380,7 +2360,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
+          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2395,6 +2375,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2661,67 +2661,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125781018</v>
+        <v>125782724</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495061</v>
+        <v>495062</v>
       </c>
       <c r="R18" t="n">
-        <v>7006152</v>
+        <v>7006173</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2750,7 +2731,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2760,7 +2741,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2775,6 +2761,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2792,48 +2798,67 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125782724</v>
+        <v>125781018</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>58021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495062</v>
+        <v>495061</v>
       </c>
       <c r="R19" t="n">
-        <v>7006173</v>
+        <v>7006152</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2862,7 +2887,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2872,12 +2897,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>21:21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2892,26 +2912,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3310,58 +3310,62 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125804779</v>
+        <v>125783073</v>
       </c>
       <c r="B23" t="n">
-        <v>98366</v>
+        <v>98345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495257</v>
+        <v>495060</v>
       </c>
       <c r="R23" t="n">
-        <v>7006101</v>
+        <v>7006169</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3385,22 +3389,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 300 plantor och 1 vinterståndare inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3414,7 +3423,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3432,62 +3441,58 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125783073</v>
+        <v>125804779</v>
       </c>
       <c r="B24" t="n">
-        <v>98345</v>
+        <v>98366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495060</v>
+        <v>495257</v>
       </c>
       <c r="R24" t="n">
-        <v>7006169</v>
+        <v>7006101</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3511,27 +3516,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>21:29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minst 300 plantor och 1 vinterståndare inom ca 3 m2 yta.</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4240,58 +4240,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125804684</v>
+        <v>125804911</v>
       </c>
       <c r="B30" t="n">
-        <v>98366</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495194</v>
+        <v>495201</v>
       </c>
       <c r="R30" t="n">
-        <v>7006084</v>
+        <v>7006107</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4320,7 +4310,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4330,7 +4320,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4345,6 +4335,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4362,7 +4372,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125803663</v>
+        <v>125804684</v>
       </c>
       <c r="B31" t="n">
         <v>98366</v>
@@ -4396,19 +4406,24 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495111</v>
+        <v>495194</v>
       </c>
       <c r="R31" t="n">
-        <v>7006101</v>
+        <v>7006084</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4437,7 +4452,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4447,7 +4462,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4479,48 +4494,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125804911</v>
+        <v>125803663</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>98366</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495201</v>
+        <v>495111</v>
       </c>
       <c r="R32" t="n">
-        <v>7006107</v>
+        <v>7006101</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4549,7 +4569,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4559,7 +4579,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4574,26 +4594,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125780777</v>
       </c>
       <c r="B2" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125782273</v>
       </c>
       <c r="B3" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>125779100</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>125778168</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>125782341</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>125783644</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125782185</v>
+        <v>125778094</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,47 +1433,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494985</v>
+        <v>495171</v>
       </c>
       <c r="R8" t="n">
-        <v>7006130</v>
+        <v>7006053</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1500,24 +1490,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,7 +1511,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1546,12 +1526,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1569,48 +1549,58 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125778094</v>
+        <v>125778932</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>98370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495171</v>
+        <v>495122</v>
       </c>
       <c r="R9" t="n">
-        <v>7006053</v>
+        <v>7006144</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1644,7 +1634,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,26 +1649,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1696,38 +1666,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125778932</v>
+        <v>125782185</v>
       </c>
       <c r="B10" t="n">
-        <v>98366</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1737,17 +1707,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495122</v>
+        <v>494985</v>
       </c>
       <c r="R10" t="n">
-        <v>7006144</v>
+        <v>7006130</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1774,14 +1744,24 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1795,7 +1775,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1816,7 +1816,7 @@
         <v>125778369</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125779205</v>
+        <v>125778852</v>
       </c>
       <c r="B12" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495123</v>
+        <v>495132</v>
       </c>
       <c r="R12" t="n">
-        <v>7006176</v>
+        <v>7006134</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125778852</v>
+        <v>125779205</v>
       </c>
       <c r="B13" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495132</v>
+        <v>495123</v>
       </c>
       <c r="R13" t="n">
-        <v>7006134</v>
+        <v>7006176</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2154,52 +2154,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125778646</v>
+        <v>125778820</v>
       </c>
       <c r="B14" t="n">
-        <v>98366</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2208,13 +2194,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495089</v>
+        <v>495134</v>
       </c>
       <c r="R14" t="n">
-        <v>7006086</v>
+        <v>7006068</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2248,7 +2234,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
+          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2263,6 +2249,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2280,38 +2286,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125778820</v>
+        <v>125778646</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>98370</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2320,13 +2340,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495134</v>
+        <v>495089</v>
       </c>
       <c r="R15" t="n">
-        <v>7006068</v>
+        <v>7006086</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2360,7 +2380,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
+          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2375,26 +2395,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2415,7 +2415,7 @@
         <v>125780666</v>
       </c>
       <c r="B16" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>125783490</v>
       </c>
       <c r="B17" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2661,48 +2661,67 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125782724</v>
+        <v>125781018</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>58025</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495062</v>
+        <v>495061</v>
       </c>
       <c r="R18" t="n">
-        <v>7006173</v>
+        <v>7006152</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2731,7 +2750,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2741,12 +2760,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>21:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2761,26 +2775,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2798,67 +2792,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125781018</v>
+        <v>125782724</v>
       </c>
       <c r="B19" t="n">
-        <v>58021</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495061</v>
+        <v>495062</v>
       </c>
       <c r="R19" t="n">
-        <v>7006152</v>
+        <v>7006173</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2887,7 +2862,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2897,7 +2872,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2912,6 +2892,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2932,7 +2932,7 @@
         <v>125782390</v>
       </c>
       <c r="B20" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>125778303</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>125780717</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>125783073</v>
       </c>
       <c r="B23" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>125804779</v>
       </c>
       <c r="B24" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>125804167</v>
       </c>
       <c r="B25" t="n">
-        <v>91234</v>
+        <v>91238</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>125803850</v>
       </c>
       <c r="B26" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>125783380</v>
       </c>
       <c r="B27" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3967,48 +3967,67 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125803426</v>
+        <v>125781629</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495064</v>
+        <v>495033</v>
       </c>
       <c r="R28" t="n">
-        <v>7006141</v>
+        <v>7006135</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4032,27 +4051,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4067,26 +4086,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4104,67 +4103,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125781629</v>
+        <v>125803426</v>
       </c>
       <c r="B29" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495033</v>
+        <v>495064</v>
       </c>
       <c r="R29" t="n">
-        <v>7006135</v>
+        <v>7006141</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4188,27 +4168,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4223,6 +4203,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4243,7 +4243,7 @@
         <v>125804911</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>125804684</v>
       </c>
       <c r="B31" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>125803663</v>
       </c>
       <c r="B32" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>125805258</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>125780529</v>
       </c>
       <c r="B34" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>125804658</v>
       </c>
       <c r="B35" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125780777</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1422,48 +1422,58 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125778094</v>
+        <v>125778932</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495171</v>
+        <v>495122</v>
       </c>
       <c r="R8" t="n">
-        <v>7006053</v>
+        <v>7006144</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1497,7 +1507,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,26 +1522,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1549,38 +1539,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125778932</v>
+        <v>125782185</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1590,17 +1580,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495122</v>
+        <v>494985</v>
       </c>
       <c r="R9" t="n">
-        <v>7006144</v>
+        <v>7006130</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1627,14 +1617,24 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,7 +1648,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1666,10 +1686,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125782185</v>
+        <v>125778094</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,47 +1697,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494985</v>
+        <v>495171</v>
       </c>
       <c r="R10" t="n">
-        <v>7006130</v>
+        <v>7006053</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1744,24 +1754,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125778852</v>
+        <v>125779205</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495132</v>
+        <v>495123</v>
       </c>
       <c r="R12" t="n">
-        <v>7006134</v>
+        <v>7006176</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125779205</v>
+        <v>125778852</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495123</v>
+        <v>495132</v>
       </c>
       <c r="R13" t="n">
-        <v>7006176</v>
+        <v>7006134</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>125778646</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>125780666</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>125783490</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2661,67 +2661,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125781018</v>
+        <v>125782724</v>
       </c>
       <c r="B18" t="n">
-        <v>58025</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495061</v>
+        <v>495062</v>
       </c>
       <c r="R18" t="n">
-        <v>7006152</v>
+        <v>7006173</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2750,7 +2731,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2760,7 +2741,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2775,6 +2761,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2792,48 +2798,67 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125782724</v>
+        <v>125781018</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>58025</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495062</v>
+        <v>495061</v>
       </c>
       <c r="R19" t="n">
-        <v>7006173</v>
+        <v>7006152</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2862,7 +2887,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2872,12 +2897,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>21:21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2892,26 +2912,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2932,7 +2932,7 @@
         <v>125782390</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>125783073</v>
       </c>
       <c r="B23" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>125804779</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>125803850</v>
       </c>
       <c r="B26" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>125783380</v>
       </c>
       <c r="B27" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>125781629</v>
       </c>
       <c r="B28" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>125804684</v>
       </c>
       <c r="B31" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>125803663</v>
       </c>
       <c r="B32" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4611,48 +4611,62 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125805258</v>
+        <v>125780529</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495123</v>
+        <v>495099</v>
       </c>
       <c r="R33" t="n">
-        <v>7006163</v>
+        <v>7006156</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4676,22 +4690,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4706,26 +4725,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4743,62 +4742,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125780529</v>
+        <v>125805258</v>
       </c>
       <c r="B34" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495099</v>
+        <v>495123</v>
       </c>
       <c r="R34" t="n">
-        <v>7006156</v>
+        <v>7006163</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4822,27 +4807,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:03</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4857,6 +4837,26 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4877,7 +4877,7 @@
         <v>125804658</v>
       </c>
       <c r="B35" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -1422,58 +1422,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125778932</v>
+        <v>125778094</v>
       </c>
       <c r="B8" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495122</v>
+        <v>495171</v>
       </c>
       <c r="R8" t="n">
-        <v>7006144</v>
+        <v>7006053</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1507,7 +1497,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,6 +1512,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1686,48 +1696,58 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125778094</v>
+        <v>125778932</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495171</v>
+        <v>495122</v>
       </c>
       <c r="R10" t="n">
-        <v>7006053</v>
+        <v>7006144</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1761,7 +1781,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1776,26 +1796,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2154,38 +2154,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125778820</v>
+        <v>125778646</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2194,13 +2208,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495134</v>
+        <v>495089</v>
       </c>
       <c r="R14" t="n">
-        <v>7006068</v>
+        <v>7006086</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2234,7 +2248,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
+          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2249,26 +2263,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2286,52 +2280,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125778646</v>
+        <v>125778820</v>
       </c>
       <c r="B15" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2340,13 +2320,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495089</v>
+        <v>495134</v>
       </c>
       <c r="R15" t="n">
-        <v>7006086</v>
+        <v>7006068</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2380,7 +2360,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
+          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2395,6 +2375,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -3967,67 +3967,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125781629</v>
+        <v>125803426</v>
       </c>
       <c r="B28" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495033</v>
+        <v>495064</v>
       </c>
       <c r="R28" t="n">
-        <v>7006135</v>
+        <v>7006141</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4051,27 +4032,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4086,6 +4067,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4103,48 +4104,67 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125803426</v>
+        <v>125781629</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495064</v>
+        <v>495033</v>
       </c>
       <c r="R29" t="n">
-        <v>7006141</v>
+        <v>7006135</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4168,27 +4188,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4203,26 +4223,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -2154,52 +2154,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125778646</v>
+        <v>125778820</v>
       </c>
       <c r="B14" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2208,13 +2194,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495089</v>
+        <v>495134</v>
       </c>
       <c r="R14" t="n">
-        <v>7006086</v>
+        <v>7006068</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2248,7 +2234,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
+          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2263,6 +2249,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2280,38 +2286,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125778820</v>
+        <v>125778646</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2320,13 +2340,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495134</v>
+        <v>495089</v>
       </c>
       <c r="R15" t="n">
-        <v>7006068</v>
+        <v>7006086</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2360,7 +2380,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
+          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2375,26 +2395,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -3310,62 +3310,58 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125783073</v>
+        <v>125804779</v>
       </c>
       <c r="B23" t="n">
-        <v>98352</v>
+        <v>98373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495060</v>
+        <v>495257</v>
       </c>
       <c r="R23" t="n">
-        <v>7006169</v>
+        <v>7006101</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3389,27 +3385,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>21:29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minst 300 plantor och 1 vinterståndare inom ca 3 m2 yta.</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3423,7 +3414,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3441,58 +3432,62 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125804779</v>
+        <v>125783073</v>
       </c>
       <c r="B24" t="n">
-        <v>98373</v>
+        <v>98352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495257</v>
+        <v>495060</v>
       </c>
       <c r="R24" t="n">
-        <v>7006101</v>
+        <v>7006169</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3516,22 +3511,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minst 300 plantor och 1 vinterståndare inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3967,48 +3967,67 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125803426</v>
+        <v>125781629</v>
       </c>
       <c r="B28" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495064</v>
+        <v>495033</v>
       </c>
       <c r="R28" t="n">
-        <v>7006141</v>
+        <v>7006135</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4032,27 +4051,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4067,26 +4086,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4104,67 +4103,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125781629</v>
+        <v>125803426</v>
       </c>
       <c r="B29" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495033</v>
+        <v>495064</v>
       </c>
       <c r="R29" t="n">
-        <v>7006135</v>
+        <v>7006141</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4188,27 +4168,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4223,6 +4203,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4240,48 +4240,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125804911</v>
+        <v>125803663</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495201</v>
+        <v>495111</v>
       </c>
       <c r="R30" t="n">
-        <v>7006107</v>
+        <v>7006101</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4310,7 +4315,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4320,7 +4325,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4335,26 +4340,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4494,53 +4479,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125803663</v>
+        <v>125804911</v>
       </c>
       <c r="B32" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495111</v>
+        <v>495201</v>
       </c>
       <c r="R32" t="n">
-        <v>7006101</v>
+        <v>7006107</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4569,7 +4549,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4579,7 +4559,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4594,6 +4574,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -1422,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125778094</v>
+        <v>125782185</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,37 +1433,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495171</v>
+        <v>494985</v>
       </c>
       <c r="R8" t="n">
-        <v>7006053</v>
+        <v>7006130</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1490,14 +1500,24 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,7 +1531,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1526,12 +1546,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1549,38 +1569,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125782185</v>
+        <v>125778932</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1590,17 +1610,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494985</v>
+        <v>495122</v>
       </c>
       <c r="R9" t="n">
-        <v>7006130</v>
+        <v>7006144</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1627,24 +1647,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1658,27 +1668,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1696,58 +1686,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125778932</v>
+        <v>125778094</v>
       </c>
       <c r="B10" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495122</v>
+        <v>495171</v>
       </c>
       <c r="R10" t="n">
-        <v>7006144</v>
+        <v>7006053</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1781,7 +1761,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1796,6 +1776,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -3313,7 +3313,7 @@
         <v>125804779</v>
       </c>
       <c r="B23" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>125783073</v>
       </c>
       <c r="B24" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>125804167</v>
       </c>
       <c r="B25" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>125803850</v>
       </c>
       <c r="B26" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>125783380</v>
       </c>
       <c r="B27" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3967,67 +3967,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125781629</v>
+        <v>125803426</v>
       </c>
       <c r="B28" t="n">
-        <v>98352</v>
+        <v>78980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495033</v>
+        <v>495064</v>
       </c>
       <c r="R28" t="n">
-        <v>7006135</v>
+        <v>7006141</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4051,27 +4032,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4086,6 +4067,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4103,48 +4104,67 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125803426</v>
+        <v>125781629</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>98361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495064</v>
+        <v>495033</v>
       </c>
       <c r="R29" t="n">
-        <v>7006141</v>
+        <v>7006135</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4168,27 +4188,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4203,26 +4223,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4240,53 +4240,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125803663</v>
+        <v>125804911</v>
       </c>
       <c r="B30" t="n">
-        <v>98373</v>
+        <v>78980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495111</v>
+        <v>495201</v>
       </c>
       <c r="R30" t="n">
-        <v>7006101</v>
+        <v>7006107</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4315,7 +4310,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4325,7 +4320,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4340,6 +4335,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4360,7 +4375,7 @@
         <v>125804684</v>
       </c>
       <c r="B31" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4479,48 +4494,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125804911</v>
+        <v>125803663</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>98382</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495201</v>
+        <v>495111</v>
       </c>
       <c r="R32" t="n">
-        <v>7006107</v>
+        <v>7006101</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4549,7 +4569,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4559,7 +4579,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4574,26 +4594,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4611,62 +4611,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125780529</v>
+        <v>125805258</v>
       </c>
       <c r="B33" t="n">
-        <v>98352</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495099</v>
+        <v>495123</v>
       </c>
       <c r="R33" t="n">
-        <v>7006156</v>
+        <v>7006163</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4690,27 +4676,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:03</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4725,6 +4706,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4742,48 +4743,62 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125805258</v>
+        <v>125780529</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>98361</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495123</v>
+        <v>495099</v>
       </c>
       <c r="R34" t="n">
-        <v>7006163</v>
+        <v>7006156</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4807,22 +4822,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4837,26 +4857,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4877,7 +4877,7 @@
         <v>125804658</v>
       </c>
       <c r="B35" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125780777</v>
+        <v>125804167</v>
       </c>
       <c r="B2" t="n">
-        <v>98373</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495044</v>
+        <v>495084</v>
       </c>
       <c r="R2" t="n">
-        <v>7006093</v>
+        <v>7006058</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +754,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fruktkropparna växer i en något smalare stående död hackspettsbearbetad gran med kådaflöden.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,6 +789,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,53 +826,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125782273</v>
+        <v>125778094</v>
       </c>
       <c r="B3" t="n">
-        <v>80116</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494977</v>
+        <v>495171</v>
       </c>
       <c r="R3" t="n">
-        <v>7006139</v>
+        <v>7006053</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,19 +894,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>21:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,27 +915,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,14 +953,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125779100</v>
+        <v>125778168</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -950,14 +984,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495094</v>
+        <v>495098</v>
       </c>
       <c r="R4" t="n">
-        <v>7006175</v>
+        <v>7006075</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,11 +1024,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,14 +1075,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125778168</v>
+        <v>125778303</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1075,19 +1104,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495098</v>
+        <v>495064</v>
       </c>
       <c r="R5" t="n">
-        <v>7006075</v>
+        <v>7006053</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,6 +1151,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Långväxta bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,14 +1207,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125782341</v>
+        <v>125778369</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1203,13 +1242,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494984</v>
+        <v>495039</v>
       </c>
       <c r="R6" t="n">
-        <v>7006135</v>
+        <v>7006046</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,24 +1275,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>21:05</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>21:05</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,7 +1296,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1305,14 +1334,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125783644</v>
+        <v>125778820</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1334,19 +1363,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495029</v>
+        <v>495134</v>
       </c>
       <c r="R7" t="n">
-        <v>7006206</v>
+        <v>7006068</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1373,24 +1407,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,6 +1429,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1422,58 +1466,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125782185</v>
+        <v>125779100</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494985</v>
+        <v>495094</v>
       </c>
       <c r="R8" t="n">
-        <v>7006130</v>
+        <v>7006175</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1500,24 +1534,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>20:53</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,7 +1555,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1546,12 +1570,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1569,55 +1593,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125778932</v>
+        <v>125780717</v>
       </c>
       <c r="B9" t="n">
-        <v>98373</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495122</v>
+        <v>495098</v>
       </c>
       <c r="R9" t="n">
-        <v>7006144</v>
+        <v>7006108</v>
       </c>
       <c r="S9" t="n">
         <v>8</v>
@@ -1647,14 +1661,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1669,6 +1688,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1686,14 +1725,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125778094</v>
+        <v>125782341</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1721,13 +1760,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495171</v>
+        <v>494984</v>
       </c>
       <c r="R10" t="n">
-        <v>7006053</v>
+        <v>7006135</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1754,11 +1793,21 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>Långväxta bålar.</t>
@@ -1775,7 +1824,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1813,14 +1862,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125778369</v>
+        <v>125782724</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1848,13 +1897,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495039</v>
+        <v>495062</v>
       </c>
       <c r="R11" t="n">
-        <v>7006046</v>
+        <v>7006173</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1881,14 +1930,24 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,7 +1961,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1940,53 +1999,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125779205</v>
+        <v>125783644</v>
       </c>
       <c r="B12" t="n">
-        <v>98373</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495123</v>
+        <v>495029</v>
       </c>
       <c r="R12" t="n">
-        <v>7006176</v>
+        <v>7006206</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2013,9 +2067,24 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2047,53 +2116,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125778852</v>
+        <v>125803426</v>
       </c>
       <c r="B13" t="n">
-        <v>98373</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495132</v>
+        <v>495064</v>
       </c>
       <c r="R13" t="n">
-        <v>7006134</v>
+        <v>7006141</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2117,12 +2181,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2136,7 +2215,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2154,14 +2253,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125778820</v>
+        <v>125804911</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2183,24 +2282,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495134</v>
+        <v>495201</v>
       </c>
       <c r="R14" t="n">
-        <v>7006068</v>
+        <v>7006107</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2224,17 +2318,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Långväxta fertila bålar på flera granar i äldre barrblandskog.</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2263,12 +2362,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2286,67 +2385,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125778646</v>
+        <v>125805129</v>
       </c>
       <c r="B15" t="n">
-        <v>98373</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495089</v>
+        <v>495175</v>
       </c>
       <c r="R15" t="n">
-        <v>7006086</v>
+        <v>7006187</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2370,17 +2450,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2395,6 +2480,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2412,58 +2517,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125780666</v>
+        <v>125805258</v>
       </c>
       <c r="B16" t="n">
-        <v>98373</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495071</v>
+        <v>495123</v>
       </c>
       <c r="R16" t="n">
-        <v>7006139</v>
+        <v>7006163</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2487,27 +2582,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 3 x 1 m2 yta.</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2522,6 +2612,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2539,10 +2649,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125783490</v>
+        <v>125782273</v>
       </c>
       <c r="B17" t="n">
-        <v>98373</v>
+        <v>80468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2550,32 +2660,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2584,10 +2689,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495008</v>
+        <v>494977</v>
       </c>
       <c r="R17" t="n">
-        <v>7006158</v>
+        <v>7006139</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2619,7 +2724,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2629,7 +2734,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2644,6 +2749,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2661,10 +2786,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125782724</v>
+        <v>125782185</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2672,37 +2797,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Bergmyren, Brynje, Kyrkås, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495062</v>
+        <v>494985</v>
       </c>
       <c r="R18" t="n">
-        <v>7006173</v>
+        <v>7006130</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2731,7 +2866,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2741,12 +2876,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, äldre. I gammal granskog med bitvis medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2775,12 +2910,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2801,7 +2936,7 @@
         <v>125781018</v>
       </c>
       <c r="B19" t="n">
-        <v>58025</v>
+        <v>58327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2929,53 +3064,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125782390</v>
+        <v>125780529</v>
       </c>
       <c r="B20" t="n">
-        <v>98373</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494971</v>
+        <v>495099</v>
       </c>
       <c r="R20" t="n">
-        <v>7006159</v>
+        <v>7006156</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3004,7 +3148,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3014,7 +3158,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3028,7 +3177,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3046,38 +3195,52 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125778303</v>
+        <v>125781629</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3086,13 +3249,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495064</v>
+        <v>495033</v>
       </c>
       <c r="R21" t="n">
-        <v>7006053</v>
+        <v>7006135</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3119,14 +3282,24 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Långväxta bålar med apothecier.</t>
+          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3140,27 +3313,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3178,45 +3331,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125780717</v>
+        <v>125783073</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495098</v>
+        <v>495060</v>
       </c>
       <c r="R22" t="n">
-        <v>7006108</v>
+        <v>7006169</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3248,7 +3415,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3258,7 +3425,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 300 plantor och 1 vinterståndare inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3272,27 +3444,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3310,38 +3462,47 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125804779</v>
+        <v>125783380</v>
       </c>
       <c r="B23" t="n">
-        <v>98382</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3351,17 +3512,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495257</v>
+        <v>495000</v>
       </c>
       <c r="R23" t="n">
-        <v>7006101</v>
+        <v>7006158</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3385,22 +3546,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>21:48</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 150 plantor inom ca  1 m2 yta.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3414,7 +3580,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3432,10 +3598,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125783073</v>
+        <v>125802946</v>
       </c>
       <c r="B24" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3462,7 +3628,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3475,19 +3641,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495060</v>
+        <v>495001</v>
       </c>
       <c r="R24" t="n">
-        <v>7006169</v>
+        <v>7006212</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3511,27 +3682,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 300 plantor och 1 vinterståndare inom ca 3 m2 yta.</t>
+          <t>Minst 120 plantor inom ca 2 x 1 m2 yta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3563,62 +3734,67 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125804167</v>
+        <v>125804658</v>
       </c>
       <c r="B25" t="n">
-        <v>91241</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>125</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495084</v>
+        <v>495202</v>
       </c>
       <c r="R25" t="n">
-        <v>7006058</v>
+        <v>7006073</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3647,7 +3823,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3657,12 +3833,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Fruktkropparna växer i en något smalare stående död hackspettsbearbetad gran med kådaflöden.</t>
+          <t>Minst 125 plantor inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3677,26 +3853,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3714,10 +3870,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125803850</v>
+        <v>125778646</v>
       </c>
       <c r="B26" t="n">
-        <v>98382</v>
+        <v>99140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3742,25 +3898,39 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495125</v>
+        <v>495089</v>
       </c>
       <c r="R26" t="n">
-        <v>7006055</v>
+        <v>7006086</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3784,22 +3954,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:09</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:09</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 14 plantor inom ca 1 m2 på mark med vitmossor och björnmossor.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3831,67 +3996,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125783380</v>
+        <v>125778852</v>
       </c>
       <c r="B27" t="n">
-        <v>98361</v>
+        <v>99140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495000</v>
+        <v>495132</v>
       </c>
       <c r="R27" t="n">
-        <v>7006158</v>
+        <v>7006134</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3918,26 +4069,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>21:48</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>21:48</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 150 plantor inom ca  1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3949,7 +4085,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3967,48 +4103,58 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125803426</v>
+        <v>125778932</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>99140</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495064</v>
+        <v>495122</v>
       </c>
       <c r="R28" t="n">
-        <v>7006141</v>
+        <v>7006144</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4032,27 +4178,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta på vitmossebädd i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4066,27 +4202,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4104,67 +4220,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125781629</v>
+        <v>125779205</v>
       </c>
       <c r="B29" t="n">
-        <v>98361</v>
+        <v>99140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495033</v>
+        <v>495123</v>
       </c>
       <c r="R29" t="n">
-        <v>7006135</v>
+        <v>7006176</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4191,26 +4293,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>20:35</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 350 plantor som växer tätt och mattbildande inom ca 1,5 m2 yta i gammal barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4222,7 +4309,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4240,48 +4327,58 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125804911</v>
+        <v>125780666</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>99140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495201</v>
+        <v>495071</v>
       </c>
       <c r="R30" t="n">
-        <v>7006107</v>
+        <v>7006139</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4305,22 +4402,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4335,26 +4437,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4372,10 +4454,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125804684</v>
+        <v>125780777</v>
       </c>
       <c r="B31" t="n">
-        <v>98382</v>
+        <v>99140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4406,21 +4488,16 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495194</v>
+        <v>495044</v>
       </c>
       <c r="R31" t="n">
-        <v>7006084</v>
+        <v>7006093</v>
       </c>
       <c r="S31" t="n">
         <v>9</v>
@@ -4447,22 +4524,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4494,10 +4561,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125803663</v>
+        <v>125782390</v>
       </c>
       <c r="B32" t="n">
-        <v>98382</v>
+        <v>99140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4534,13 +4601,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495111</v>
+        <v>494971</v>
       </c>
       <c r="R32" t="n">
-        <v>7006101</v>
+        <v>7006159</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4564,22 +4631,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4593,7 +4660,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4611,45 +4678,55 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125805258</v>
+        <v>125783490</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>99140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495123</v>
+        <v>495008</v>
       </c>
       <c r="R33" t="n">
-        <v>7006163</v>
+        <v>7006158</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -4676,22 +4753,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4705,27 +4782,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4743,62 +4800,58 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125780529</v>
+        <v>125783596</v>
       </c>
       <c r="B34" t="n">
-        <v>98361</v>
+        <v>99140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495099</v>
+        <v>495014</v>
       </c>
       <c r="R34" t="n">
-        <v>7006156</v>
+        <v>7006211</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4827,7 +4880,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4837,12 +4890,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:03</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Minst 195 plantor fläckvis inom ca 8 m2 yta i äldre barrskog.</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4874,67 +4922,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125804658</v>
+        <v>125803663</v>
       </c>
       <c r="B35" t="n">
-        <v>98361</v>
+        <v>99140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495202</v>
+        <v>495111</v>
       </c>
       <c r="R35" t="n">
-        <v>7006073</v>
+        <v>7006101</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4963,7 +4997,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4973,12 +5007,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Minst 125 plantor inom ca 2 x 1 m2 yta.</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5007,6 +5036,367 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125803850</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bergmyren, Bergmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>495125</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7006055</v>
+      </c>
+      <c r="S36" t="n">
+        <v>7</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125804684</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>495194</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7006084</v>
+      </c>
+      <c r="S37" t="n">
+        <v>9</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125804779</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Barnsängbäcken, Barnsängbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>495257</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7006101</v>
+      </c>
+      <c r="S38" t="n">
+        <v>7</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26372-2025 artfynd.xlsx
+++ b/artfynd/A 26372-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -823,6 +828,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125804167</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -950,6 +960,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125778094</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1072,6 +1087,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125778168</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1204,6 +1224,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125778303</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1331,6 +1356,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125778369</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1463,6 +1493,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125778820</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1590,6 +1625,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125779100</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1722,6 +1762,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125780717</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1859,6 +1904,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125782341</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1996,6 +2046,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125782724</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2113,6 +2168,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125783644</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2250,6 +2310,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125803426</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2382,6 +2447,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125804911</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2514,6 +2584,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125805129</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2646,6 +2721,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125805258</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2783,6 +2863,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125782273</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2930,6 +3015,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125782185</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3061,6 +3151,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125781018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3192,6 +3287,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125780529</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3328,6 +3428,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125781629</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3459,6 +3564,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125783073</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3595,6 +3705,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125783380</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3731,6 +3846,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125802946</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3867,6 +3987,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125804658</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3993,6 +4118,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125778646</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4100,6 +4230,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125778852</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4217,6 +4352,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125778932</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4324,6 +4464,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125779205</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4451,6 +4596,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125780666</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4558,6 +4708,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125780777</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4675,6 +4830,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125782390</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4797,6 +4957,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125783490</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4919,6 +5084,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125783596</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5036,6 +5206,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125803663</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5153,6 +5328,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125803850</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5275,6 +5455,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125804684</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5397,8 +5582,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125804779</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>